--- a/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
+++ b/Fase 2/SIGMA_Product_Backlog_por_Sprint.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\SIGMA\Fase 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F106E3A0-168B-4CC5-9293-5DD642113901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3718EF2A-3705-4E30-99C1-DD1EA58D495D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
@@ -2514,7 +2514,7 @@
     <t>Total Sprint 6</t>
   </si>
   <si>
-    <t>132 historias de usuario · 751 puntos · 20 épicas</t>
+    <t>138 historias de usuario · 785 puntos · 20 épicas</t>
   </si>
   <si>
     <t>Nombre de la épica</t>
@@ -40744,11 +40744,11 @@
         <v>44</v>
       </c>
       <c r="D8" s="9">
-        <f>SUM('Sprint 3'!$I$6:$I$28)</f>
-        <v>118</v>
+        <f>SUM('Sprint 3'!$I$6:$I$34)</f>
+        <v>152</v>
       </c>
       <c r="E8" s="9">
-        <f>SUM('Sprint 3'!$O$6:$O$28)</f>
+        <f>SUM('Sprint 3'!$O$6:$O$34)</f>
         <v>0</v>
       </c>
       <c r="F8" s="11">
@@ -40756,24 +40756,24 @@
         <v>0</v>
       </c>
       <c r="G8" s="9">
-        <f>COUNTA('Sprint 3'!$A$6:$A$28)</f>
-        <v>23</v>
+        <f>COUNTA('Sprint 3'!$A$6:$A$34)</f>
+        <v>29</v>
       </c>
       <c r="H8" s="9">
-        <f>COUNTIF('Sprint 3'!$M$6:$M$28,"Terminada")</f>
+        <f>COUNTIF('Sprint 3'!$M$6:$M$34,"Terminada")</f>
         <v>0</v>
       </c>
       <c r="I8" s="9">
-        <f>COUNTIF('Sprint 3'!$M$6:$M$28,"En curso")</f>
-        <v>0</v>
+        <f>COUNTIF('Sprint 3'!$M$6:$M$34,"En curso")</f>
+        <v>6</v>
       </c>
       <c r="J8" s="9">
-        <f>COUNTIF('Sprint 3'!$M$6:$M$28,"Bloqueada")</f>
+        <f>COUNTIF('Sprint 3'!$M$6:$M$34,"Bloqueada")</f>
         <v>0</v>
       </c>
       <c r="K8" s="9">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40913,7 +40913,7 @@
       <c r="C12" s="15"/>
       <c r="D12" s="15">
         <f>SUM(D6:D11)</f>
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="E12" s="15">
         <f>SUM(E6:E11)</f>
@@ -40925,7 +40925,7 @@
       </c>
       <c r="G12" s="15">
         <f>SUM(G6:G11)</f>
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H12" s="15">
         <f>SUM(H6:H11)</f>
@@ -40933,7 +40933,7 @@
       </c>
       <c r="I12" s="15">
         <f>SUM(I6:I11)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12" s="15">
         <f>SUM(J6:J11)</f>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="K12" s="15">
         <f>SUM(K6:K11)</f>
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44464,42 +44464,42 @@
         <v>30</v>
       </c>
       <c r="B3" s="20">
-        <f>COUNTA($A$6:$A$28)</f>
-        <v>23</v>
+        <f>COUNTA($A$6:$A$34)</f>
+        <v>29</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>163</v>
       </c>
       <c r="D3" s="20">
-        <f>SUM($I$6:$I$28)</f>
-        <v>118</v>
+        <f>SUM($I$6:$I$34)</f>
+        <v>152</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>164</v>
       </c>
       <c r="F3" s="20">
-        <f>SUM($O$6:$O$28)</f>
+        <f>SUM($O$6:$O$34)</f>
         <v>0</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>33</v>
       </c>
       <c r="H3" s="21">
-        <f>IFERROR(SUM($O$6:$O$28)/SUM($I$6:$I$28),0)</f>
+        <f>IFERROR(SUM($O$6:$O$34)/SUM($I$6:$I$34),0)</f>
         <v>0</v>
       </c>
       <c r="I3" s="19" t="s">
         <v>165</v>
       </c>
       <c r="J3" s="20">
-        <f>COUNTIF($M$6:$M$28,"Terminada")</f>
+        <f>COUNTIF($M$6:$M$34,"Terminada")</f>
         <v>0</v>
       </c>
       <c r="K3" s="19" t="s">
         <v>166</v>
       </c>
       <c r="L3" s="20">
-        <f>COUNTIF($M$6:$M$28,"Bloqueada")</f>
+        <f>COUNTIF($M$6:$M$34,"Bloqueada")</f>
         <v>0</v>
       </c>
     </row>
